--- a/ValueSet-no-ich-treatment-reason-vs.xlsx
+++ b/ValueSet-no-ich-treatment-reason-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-07T11:15:53+00:00</t>
+    <t>2026-05-08T09:03:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-no-ich-treatment-reason-vs.xlsx
+++ b/ValueSet-no-ich-treatment-reason-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-08T09:03:17+00:00</t>
+    <t>2026-05-08T09:31:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-no-ich-treatment-reason-vs.xlsx
+++ b/ValueSet-no-ich-treatment-reason-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-08T09:31:23+00:00</t>
+    <t>2026-05-08T10:13:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-no-ich-treatment-reason-vs.xlsx
+++ b/ValueSet-no-ich-treatment-reason-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-08T10:13:17+00:00</t>
+    <t>2026-05-11T15:54:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -85,7 +85,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Allowed coded values for NoIchTreatmentReason, generated from enum_models.py.</t>
+    <t>Allowed coded values for NoIchTreatmentReason</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/ValueSet-no-ich-treatment-reason-vs.xlsx
+++ b/ValueSet-no-ich-treatment-reason-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-11T15:54:34+00:00</t>
+    <t>2026-05-11T15:54:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-no-ich-treatment-reason-vs.xlsx
+++ b/ValueSet-no-ich-treatment-reason-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-11T15:54:44+00:00</t>
+    <t>2026-05-12T07:59:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-no-ich-treatment-reason-vs.xlsx
+++ b/ValueSet-no-ich-treatment-reason-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-12T07:59:38+00:00</t>
+    <t>2026-05-12T09:41:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-no-ich-treatment-reason-vs.xlsx
+++ b/ValueSet-no-ich-treatment-reason-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-12T09:41:56+00:00</t>
+    <t>2026-05-12T11:55:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-no-ich-treatment-reason-vs.xlsx
+++ b/ValueSet-no-ich-treatment-reason-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-12T11:55:23+00:00</t>
+    <t>2026-05-13T14:14:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-no-ich-treatment-reason-vs.xlsx
+++ b/ValueSet-no-ich-treatment-reason-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-13T14:14:43+00:00</t>
+    <t>2026-05-13T15:23:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-no-ich-treatment-reason-vs.xlsx
+++ b/ValueSet-no-ich-treatment-reason-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-13T15:23:44+00:00</t>
+    <t>2026-05-14T08:09:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-no-ich-treatment-reason-vs.xlsx
+++ b/ValueSet-no-ich-treatment-reason-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-14T08:09:55+00:00</t>
+    <t>2026-05-14T08:55:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-no-ich-treatment-reason-vs.xlsx
+++ b/ValueSet-no-ich-treatment-reason-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-14T08:55:50+00:00</t>
+    <t>2026-05-14T09:35:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-no-ich-treatment-reason-vs.xlsx
+++ b/ValueSet-no-ich-treatment-reason-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-14T09:35:04+00:00</t>
+    <t>2026-05-14T11:02:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-no-ich-treatment-reason-vs.xlsx
+++ b/ValueSet-no-ich-treatment-reason-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-14T11:02:20+00:00</t>
+    <t>2026-05-15T10:10:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
